--- a/consent_forms/045_iv_therapy_injections_consent_form--consent_forms.xlsx
+++ b/consent_forms/045_iv_therapy_injections_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,12 +711,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -744,12 +744,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'penicillin'}</t>
+          <t>penicillin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Penicillin'}</t>
+          <t>Penicillin</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -778,12 +778,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -795,12 +795,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'name',_'label':_'name',_'type':_'text'}</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Name', 'label': 'Name', 'type': 'text'}</t>
+          <t>Name</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'phone',_'label':_'phone',_'type':_'text'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Phone', 'label': 'Phone', 'type': 'text'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'email',_'label':_'email',_'type':_'text'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Email', 'label': 'Email', 'type': 'text'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'address',_'label':_'address',_'type':_'text'}</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Address', 'label': 'Address', 'type': 'text'}</t>
+          <t>Address</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'relationship',_'label':_'relationship',_'type':_'text'}</t>
+          <t>relationship</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Relationship', 'label': 'Relationship', 'type': 'text'}</t>
+          <t>Relationship</t>
         </is>
       </c>
     </row>
@@ -880,63 +880,63 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'contact',_'label':_'contact',_'type':_'text'}</t>
+          <t>contact</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Contact', 'label': 'Contact', 'type': 'text'}</t>
+          <t>Contact</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>emergency_contacts_choices</t>
+          <t>consent_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'phone',_'label':_'phone',_'type':_'text'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Phone', 'label': 'Phone', 'type': 'text'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>emergency_contacts_choices</t>
+          <t>consent_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'email',_'label':_'email',_'type':_'text'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Email', 'label': 'Email', 'type': 'text'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>emergency_contacts_choices</t>
+          <t>consent_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'address',_'label':_'address',_'type':_'text'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'Address', 'label': 'Address', 'type': 'text'}</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true,_'type':_'text'}</t>
+          <t>not_now</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True, 'type': 'text'}</t>
+          <t>Not Now</t>
         </is>
       </c>
     </row>
@@ -965,63 +965,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>consent_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'maybe',_'label':_'maybe'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'Maybe', 'label': 'Maybe'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>consent_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'id':_10,_'name':_'not_now',_'label':_'not_now'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'id': 10, 'name': 'Not Now', 'label': 'Not Now'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>consent_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'id':_11,_'name':_'other',_'label':_'other',_'type':_'text'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'id': 11, 'name': 'Other', 'label': 'Other', 'type': 'text'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
